--- a/Config/Excel/skill/ability_segment_effect.xlsx
+++ b/Config/Excel/skill/ability_segment_effect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -37,6 +37,9 @@
     <t>formulaType</t>
   </si>
   <si>
+    <t>formulaValue</t>
+  </si>
+  <si>
     <t>baseValue</t>
   </si>
   <si>
@@ -67,16 +70,25 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>1,5000</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
+    <t>3,5000</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
-    <t>1,4000</t>
+    <t>3,4000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>200001</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -692,15 +704,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1019,21 +1028,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="2" customWidth="1"/>
-    <col min="5" max="6" width="19.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="19.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1057,123 +1066,141 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+    <row r="4" spans="1:10">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>130000</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>130001</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>130002</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>130003</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>130004</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>130005</v>
       </c>
@@ -1183,7 +1210,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I4 A5:D5 G5:I5 A6:B6 F6:I6 A7:I10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Config/Excel/skill/ability_segment_effect.xlsx
+++ b/Config/Excel/skill/ability_segment_effect.xlsx
@@ -28,8 +28,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1、造成伤害
+2、添加buff</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -40,6 +73,9 @@
     <t>formulaValue</t>
   </si>
   <si>
+    <t>damageType</t>
+  </si>
+  <si>
     <t>baseValue</t>
   </si>
   <si>
@@ -70,6 +106,33 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>公式类型</t>
+  </si>
+  <si>
+    <t>公式值</t>
+  </si>
+  <si>
+    <t>伤害类型</t>
+  </si>
+  <si>
+    <t>基础值</t>
+  </si>
+  <si>
+    <t>参数1</t>
+  </si>
+  <si>
+    <t>参数2</t>
+  </si>
+  <si>
+    <t>参数3</t>
+  </si>
+  <si>
+    <t>参数4</t>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -85,7 +148,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>200001</t>
+    <t>190001</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>3</t>
@@ -101,7 +167,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +318,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1028,20 +1105,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="17" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
-    <col min="6" max="7" width="19.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
+    <col min="3" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="19.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1069,80 +1146,116 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>130000</v>
       </c>
@@ -1150,57 +1263,66 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>130001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>130002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>130003</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>130004</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>130005</v>
       </c>
@@ -1210,8 +1332,9 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J10" numberStoredAsText="1"/>
+    <ignoredError sqref="F7:K10 F1:K3 F5:K6 D1 C2:D3 C5:D6 A8:D10 A7:C7 A1:B6" numberStoredAsText="1"/>
   </ignoredErrors>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Config/Excel/skill/ability_segment_effect.xlsx
+++ b/Config/Excel/skill/ability_segment_effect.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="D4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,20 +62,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>elementType</t>
+  </si>
+  <si>
     <t>formulaType</t>
   </si>
   <si>
     <t>formulaValue</t>
   </si>
   <si>
-    <t>damageType</t>
-  </si>
-  <si>
     <t>baseValue</t>
   </si>
   <si>
@@ -106,15 +106,15 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>元素类型</t>
+  </si>
+  <si>
     <t>公式类型</t>
   </si>
   <si>
     <t>公式值</t>
   </si>
   <si>
-    <t>伤害类型</t>
-  </si>
-  <si>
     <t>基础值</t>
   </si>
   <si>
@@ -133,28 +133,46 @@
     <t>参数5</t>
   </si>
   <si>
+    <t>130000</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>3,5000</t>
   </si>
   <si>
+    <t>130001</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
     <t>3,4000</t>
   </si>
   <si>
+    <t>130002</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>190001</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>130003</t>
+  </si>
+  <si>
+    <t>130004</t>
+  </si>
+  <si>
+    <t>130005</t>
   </si>
 </sst>
 </file>
@@ -1256,75 +1274,75 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1">
-        <v>130000</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1">
         <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1">
-        <v>130001</v>
+      <c r="A6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1">
-        <v>130002</v>
+      <c r="A7" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1">
-        <v>130003</v>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1">
-        <v>130004</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1">
-        <v>130005</v>
+      <c r="A10" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1332,7 +1350,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F7:K10 F1:K3 F5:K6 D1 C2:D3 C5:D6 A8:D10 A7:C7 A1:B6" numberStoredAsText="1"/>
+    <ignoredError sqref="D8:E10 D5:E6 D7 A1:B4 B5:B10 D2:K3 H1:K1 F5:K10" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
